--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,6 +1623,601 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122385123</v>
+      </c>
+      <c r="B11" t="n">
+        <v>55974</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563206</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7040497</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122385265</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563235</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7040529</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122385230</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563239</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7040529</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122384968</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flarmyran, Flarmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>563159</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7040597</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122385195</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Renmyran, Renmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>563228</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7040502</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385123</v>
+        <v>122385195</v>
       </c>
       <c r="B11" t="n">
-        <v>55974</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,39 +1641,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563206</v>
+        <v>563228</v>
       </c>
       <c r="R11" t="n">
-        <v>7040497</v>
+        <v>7040502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1700,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1715,7 +1710,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,7 +1737,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385265</v>
+        <v>122385230</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1778,7 +1773,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1787,7 +1782,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563235</v>
+        <v>563239</v>
       </c>
       <c r="R12" t="n">
         <v>7040529</v>
@@ -1822,7 +1817,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,12 +1827,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,19 +1847,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385230</v>
+        <v>122384968</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1905,14 +1900,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563239</v>
+        <v>563159</v>
       </c>
       <c r="R13" t="n">
-        <v>7040529</v>
+        <v>7040597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1939,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1954,7 +1949,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1986,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122384968</v>
+        <v>122385123</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>55974</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,21 +1997,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,14 +2022,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563159</v>
+        <v>563206</v>
       </c>
       <c r="R14" t="n">
-        <v>7040597</v>
+        <v>7040497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2061,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2076,12 +2071,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385195</v>
+        <v>122385265</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,34 +2114,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563228</v>
+        <v>563235</v>
       </c>
       <c r="R15" t="n">
-        <v>7040502</v>
+        <v>7040529</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2188,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,12 +2208,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1737,7 +1737,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385230</v>
+        <v>122385265</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1773,7 +1773,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563239</v>
+        <v>563235</v>
       </c>
       <c r="R12" t="n">
         <v>7040529</v>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385265</v>
+        <v>122385230</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2134,7 +2134,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563235</v>
+        <v>563239</v>
       </c>
       <c r="R15" t="n">
         <v>7040529</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,12 +2208,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385195</v>
+        <v>122385265</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,34 +1641,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563228</v>
+        <v>563235</v>
       </c>
       <c r="R11" t="n">
-        <v>7040502</v>
+        <v>7040529</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1705,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1710,7 +1715,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,22 +1735,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385265</v>
+        <v>122385230</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,7 +1783,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1782,7 +1792,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563235</v>
+        <v>563239</v>
       </c>
       <c r="R12" t="n">
         <v>7040529</v>
@@ -1817,7 +1827,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1827,12 +1837,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,22 +1857,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122384968</v>
+        <v>122385123</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>55979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,14 +1910,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563159</v>
+        <v>563206</v>
       </c>
       <c r="R13" t="n">
-        <v>7040597</v>
+        <v>7040497</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1949,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1949,12 +1959,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,10 +1986,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385123</v>
+        <v>122384968</v>
       </c>
       <c r="B14" t="n">
-        <v>55974</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,21 +2002,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,14 +2027,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563206</v>
+        <v>563159</v>
       </c>
       <c r="R14" t="n">
-        <v>7040497</v>
+        <v>7040597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2066,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2071,7 +2076,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385230</v>
+        <v>122385195</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2114,39 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563239</v>
+        <v>563228</v>
       </c>
       <c r="R15" t="n">
-        <v>7040529</v>
+        <v>7040502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,12 +2193,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385265</v>
+        <v>122385195</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,39 +1641,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563235</v>
+        <v>563228</v>
       </c>
       <c r="R11" t="n">
-        <v>7040529</v>
+        <v>7040502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1700,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1715,12 +1710,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,19 +1725,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385230</v>
+        <v>122385265</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1783,7 +1773,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1792,7 +1782,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563239</v>
+        <v>563235</v>
       </c>
       <c r="R12" t="n">
         <v>7040529</v>
@@ -1827,7 +1817,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1837,12 +1827,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,22 +1847,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385123</v>
+        <v>122385230</v>
       </c>
       <c r="B13" t="n">
-        <v>55979</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,21 +1875,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1914,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563206</v>
+        <v>563239</v>
       </c>
       <c r="R13" t="n">
-        <v>7040497</v>
+        <v>7040529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1939,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1959,7 +1949,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122384968</v>
+        <v>122385123</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>55979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,21 +1997,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,14 +2022,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563159</v>
+        <v>563206</v>
       </c>
       <c r="R14" t="n">
-        <v>7040597</v>
+        <v>7040497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2061,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2076,12 +2071,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385195</v>
+        <v>122384968</v>
       </c>
       <c r="B15" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,34 +2114,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563228</v>
+        <v>563159</v>
       </c>
       <c r="R15" t="n">
-        <v>7040502</v>
+        <v>7040597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2188,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385195</v>
+        <v>122385123</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>55979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,34 +1641,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>206004</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563228</v>
+        <v>563206</v>
       </c>
       <c r="R11" t="n">
-        <v>7040502</v>
+        <v>7040497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,7 +1737,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385265</v>
+        <v>122385230</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1755,11 +1755,6 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1773,7 +1768,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1782,7 +1777,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563235</v>
+        <v>563239</v>
       </c>
       <c r="R12" t="n">
         <v>7040529</v>
@@ -1817,7 +1812,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1827,12 +1822,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,22 +1842,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385230</v>
+        <v>122385195</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,39 +1870,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563239</v>
+        <v>563228</v>
       </c>
       <c r="R13" t="n">
-        <v>7040529</v>
+        <v>7040502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1924,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1949,12 +1934,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385123</v>
+        <v>122385265</v>
       </c>
       <c r="B14" t="n">
-        <v>55979</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,27 +1977,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Skogshare</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2026,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563206</v>
+        <v>563235</v>
       </c>
       <c r="R14" t="n">
-        <v>7040497</v>
+        <v>7040529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2036,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2071,7 +2046,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,12 +2066,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2115,11 +2095,6 @@
       </c>
       <c r="E15" t="n">
         <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385123</v>
+        <v>122385230</v>
       </c>
       <c r="B11" t="n">
-        <v>55979</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,16 +1641,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1665,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563206</v>
+        <v>563239</v>
       </c>
       <c r="R11" t="n">
-        <v>7040497</v>
+        <v>7040529</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1705,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1710,7 +1715,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385230</v>
+        <v>122385123</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>55983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,16 +1763,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>206004</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563239</v>
+        <v>563206</v>
       </c>
       <c r="R12" t="n">
-        <v>7040529</v>
+        <v>7040497</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1827,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1822,12 +1837,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385195</v>
+        <v>122385265</v>
       </c>
       <c r="B13" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,29 +1880,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563228</v>
+        <v>563235</v>
       </c>
       <c r="R13" t="n">
-        <v>7040502</v>
+        <v>7040529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,7 +1944,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1934,7 +1954,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,22 +1974,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385265</v>
+        <v>122384968</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,6 +2004,11 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1992,19 +2022,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563235</v>
+        <v>563159</v>
       </c>
       <c r="R14" t="n">
-        <v>7040529</v>
+        <v>7040597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2066,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2046,12 +2076,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,22 +2096,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122384968</v>
+        <v>122385195</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,34 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563159</v>
+        <v>563228</v>
       </c>
       <c r="R15" t="n">
-        <v>7040597</v>
+        <v>7040502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2163,12 +2193,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,7 +1625,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385230</v>
+        <v>122385265</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1661,7 +1661,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563239</v>
+        <v>563235</v>
       </c>
       <c r="R11" t="n">
         <v>7040529</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,22 +1735,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385123</v>
+        <v>122385195</v>
       </c>
       <c r="B12" t="n">
-        <v>55983</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,39 +1763,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563206</v>
+        <v>563228</v>
       </c>
       <c r="R12" t="n">
-        <v>7040497</v>
+        <v>7040502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1837,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,7 +1859,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385265</v>
+        <v>122385230</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1900,7 +1895,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1909,7 +1904,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563235</v>
+        <v>563239</v>
       </c>
       <c r="R13" t="n">
         <v>7040529</v>
@@ -1944,7 +1939,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1954,12 +1949,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,12 +1969,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385195</v>
+        <v>122385123</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>55983</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,34 +2119,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563228</v>
+        <v>563206</v>
       </c>
       <c r="R15" t="n">
-        <v>7040502</v>
+        <v>7040497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1747,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385195</v>
+        <v>122384968</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,34 +1763,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563228</v>
+        <v>563159</v>
       </c>
       <c r="R12" t="n">
-        <v>7040502</v>
+        <v>7040597</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1827,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1837,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385230</v>
+        <v>122385195</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,39 +1885,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563239</v>
+        <v>563228</v>
       </c>
       <c r="R13" t="n">
-        <v>7040529</v>
+        <v>7040502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1944,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1949,12 +1954,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122384968</v>
+        <v>122385230</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2022,14 +2022,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563159</v>
+        <v>563239</v>
       </c>
       <c r="R14" t="n">
-        <v>7040597</v>
+        <v>7040529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1747,7 +1747,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122384968</v>
+        <v>122385230</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1788,14 +1788,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563159</v>
+        <v>563239</v>
       </c>
       <c r="R12" t="n">
-        <v>7040597</v>
+        <v>7040529</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385195</v>
+        <v>122384968</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,34 +1885,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563228</v>
+        <v>563159</v>
       </c>
       <c r="R13" t="n">
-        <v>7040502</v>
+        <v>7040597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1949,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1954,7 +1959,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,10 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385230</v>
+        <v>122385123</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>55983</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,21 +2007,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2026,10 +2036,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563239</v>
+        <v>563206</v>
       </c>
       <c r="R14" t="n">
-        <v>7040529</v>
+        <v>7040497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2071,12 +2081,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385123</v>
+        <v>122385195</v>
       </c>
       <c r="B15" t="n">
-        <v>55983</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,39 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563206</v>
+        <v>563228</v>
       </c>
       <c r="R15" t="n">
-        <v>7040497</v>
+        <v>7040502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385265</v>
+        <v>122385195</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,39 +1641,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563235</v>
+        <v>563228</v>
       </c>
       <c r="R11" t="n">
-        <v>7040529</v>
+        <v>7040502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1700,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1715,12 +1710,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,19 +1725,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385230</v>
+        <v>122385265</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1783,7 +1773,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1792,7 +1782,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563239</v>
+        <v>563235</v>
       </c>
       <c r="R12" t="n">
         <v>7040529</v>
@@ -1827,7 +1817,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1837,12 +1827,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,19 +1847,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122384968</v>
+        <v>122385230</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1910,14 +1900,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563159</v>
+        <v>563239</v>
       </c>
       <c r="R13" t="n">
-        <v>7040597</v>
+        <v>7040529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1939,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1959,7 +1949,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1991,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385123</v>
+        <v>122384968</v>
       </c>
       <c r="B14" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2007,21 +1997,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,14 +2022,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563206</v>
+        <v>563159</v>
       </c>
       <c r="R14" t="n">
-        <v>7040497</v>
+        <v>7040597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,7 +2061,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,7 +2071,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385195</v>
+        <v>122385123</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>55983</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,34 +2119,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563228</v>
+        <v>563206</v>
       </c>
       <c r="R15" t="n">
-        <v>7040502</v>
+        <v>7040497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1628,7 +1628,7 @@
         <v>122385195</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>122385265</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385230</v>
+        <v>122385123</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>55984</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,21 +1875,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563239</v>
+        <v>563206</v>
       </c>
       <c r="R13" t="n">
-        <v>7040529</v>
+        <v>7040497</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1949,12 +1949,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122384968</v>
+        <v>122385230</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,14 +2017,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563159</v>
+        <v>563239</v>
       </c>
       <c r="R14" t="n">
-        <v>7040597</v>
+        <v>7040529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2056,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2071,7 +2066,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2103,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385123</v>
+        <v>122384968</v>
       </c>
       <c r="B15" t="n">
-        <v>55983</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,21 +2114,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,14 +2139,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563206</v>
+        <v>563159</v>
       </c>
       <c r="R15" t="n">
-        <v>7040497</v>
+        <v>7040597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2188,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385195</v>
+        <v>122385123</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>55984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,34 +1641,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563228</v>
+        <v>563206</v>
       </c>
       <c r="R11" t="n">
-        <v>7040502</v>
+        <v>7040497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1705,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1710,7 +1715,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385265</v>
+        <v>122385195</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,39 +1758,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563235</v>
+        <v>563228</v>
       </c>
       <c r="R12" t="n">
-        <v>7040529</v>
+        <v>7040502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1827,12 +1827,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,22 +1842,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385123</v>
+        <v>122384968</v>
       </c>
       <c r="B13" t="n">
-        <v>55984</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,14 +1895,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563206</v>
+        <v>563159</v>
       </c>
       <c r="R13" t="n">
-        <v>7040497</v>
+        <v>7040597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1934,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1949,7 +1944,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122384968</v>
+        <v>122385265</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2134,19 +2134,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563159</v>
+        <v>563235</v>
       </c>
       <c r="R15" t="n">
-        <v>7040597</v>
+        <v>7040529</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,12 +2208,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385123</v>
+        <v>122385230</v>
       </c>
       <c r="B11" t="n">
-        <v>55984</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,21 +1641,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563206</v>
+        <v>563239</v>
       </c>
       <c r="R11" t="n">
-        <v>7040497</v>
+        <v>7040529</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1715,7 +1715,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385195</v>
+        <v>122384968</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,34 +1763,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563228</v>
+        <v>563159</v>
       </c>
       <c r="R12" t="n">
-        <v>7040502</v>
+        <v>7040597</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1827,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1827,7 +1837,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,7 +1869,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122384968</v>
+        <v>122385265</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1890,19 +1905,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flarmyran, Flarmyran, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563159</v>
+        <v>563235</v>
       </c>
       <c r="R13" t="n">
-        <v>7040597</v>
+        <v>7040529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1949,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1944,12 +1959,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,22 +1979,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385230</v>
+        <v>122385123</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>55984</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,21 +2007,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2021,10 +2036,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563239</v>
+        <v>563206</v>
       </c>
       <c r="R14" t="n">
-        <v>7040529</v>
+        <v>7040497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2066,12 +2081,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385265</v>
+        <v>122385195</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2114,39 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563235</v>
+        <v>563228</v>
       </c>
       <c r="R15" t="n">
-        <v>7040529</v>
+        <v>7040502</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,12 +2193,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,12 +2208,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111630874</v>
+        <v>119402602</v>
       </c>
       <c r="B2" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håsjön, Ång</t>
+          <t>Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563367</v>
+        <v>563327</v>
       </c>
       <c r="R2" t="n">
-        <v>7040277</v>
+        <v>7040488</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119402607</v>
+        <v>111630874</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,14 +807,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Håsjöån, Ång</t>
+          <t>Håsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563340</v>
+        <v>563366</v>
       </c>
       <c r="R3" t="n">
-        <v>7040411</v>
+        <v>7040276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,31 +861,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119402604</v>
+        <v>119402606</v>
       </c>
       <c r="B4" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563060</v>
+        <v>563325</v>
       </c>
       <c r="R4" t="n">
-        <v>7040650</v>
+        <v>7040447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119402602</v>
+        <v>119402607</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563327</v>
+        <v>563340</v>
       </c>
       <c r="R5" t="n">
-        <v>7040488</v>
+        <v>7040411</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,19 +1075,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119402608</v>
+        <v>119402600</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1135,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563329</v>
+        <v>563250</v>
       </c>
       <c r="R6" t="n">
-        <v>7040408</v>
+        <v>7040571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,16 +1179,11 @@
         <v>119402601</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1307,19 +1277,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119402600</v>
+        <v>119402608</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1347,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563250</v>
+        <v>563329</v>
       </c>
       <c r="R8" t="n">
-        <v>7040571</v>
+        <v>7040408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,50 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119402605</v>
+        <v>122385195</v>
       </c>
       <c r="B9" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håsjöån, Ång</t>
+          <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563326</v>
+        <v>563228</v>
       </c>
       <c r="R9" t="n">
-        <v>7040479</v>
+        <v>7040502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,12 +1443,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,31 +1473,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119402606</v>
+        <v>119402604</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,21 +1496,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563325</v>
+        <v>563060</v>
       </c>
       <c r="R10" t="n">
-        <v>7040447</v>
+        <v>7040650</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,15 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385230</v>
+        <v>119402605</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,39 +1597,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renmyran, Renmyran, Ång</t>
+          <t>Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563239</v>
+        <v>563326</v>
       </c>
       <c r="R11" t="n">
-        <v>7040529</v>
+        <v>7040479</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,27 +1651,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,27 +1671,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>122384968</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,15 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385265</v>
+        <v>122385230</v>
       </c>
       <c r="B13" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1835,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1914,7 +1844,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563235</v>
+        <v>563239</v>
       </c>
       <c r="R13" t="n">
         <v>7040529</v>
@@ -1949,7 +1879,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1959,12 +1889,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,27 +1909,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385123</v>
+        <v>122385265</v>
       </c>
       <c r="B14" t="n">
-        <v>55984</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,27 +1932,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2036,10 +1961,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563206</v>
+        <v>563235</v>
       </c>
       <c r="R14" t="n">
-        <v>7040497</v>
+        <v>7040529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,7 +2006,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,27 +2026,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122385195</v>
+        <v>122385123</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,34 +2049,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Renmyran, Renmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563228</v>
+        <v>563206</v>
       </c>
       <c r="R15" t="n">
-        <v>7040502</v>
+        <v>7040497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2113,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2123,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 61541-2024 artfynd.xlsx
+++ b/artfynd/A 61541-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402606</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402607</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402601</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402608</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122385195</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402604</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1684,6 +1734,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402605</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1801,6 +1856,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122384968</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122385230</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2035,6 +2100,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122385265</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,8 +2217,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122385123</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>